--- a/backend/data/financials_by_company/1GXI.MI.xlsx
+++ b/backend/data/financials_by_company/1GXI.MI.xlsx
@@ -682,630 +682,630 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45626</v>
+        <v>44530</v>
       </c>
       <c r="B2" t="n">
-        <v>-8157085</v>
+        <v>-13152798</v>
       </c>
       <c r="C2" t="n">
-        <v>0.235</v>
+        <v>0.318</v>
       </c>
       <c r="D2" t="n">
-        <v>440681000</v>
+        <v>335287000</v>
       </c>
       <c r="E2" t="n">
-        <v>-34711000</v>
+        <v>-41361000</v>
       </c>
       <c r="F2" t="n">
-        <v>-34711000</v>
+        <v>-41361000</v>
       </c>
       <c r="G2" t="n">
-        <v>109720000</v>
+        <v>83788000</v>
       </c>
       <c r="H2" t="n">
-        <v>198532000</v>
+        <v>145359000</v>
       </c>
       <c r="I2" t="n">
-        <v>1428138000</v>
+        <v>1051685000</v>
       </c>
       <c r="J2" t="n">
-        <v>405970000</v>
+        <v>293926000</v>
       </c>
       <c r="K2" t="n">
-        <v>207438000</v>
+        <v>148567000</v>
       </c>
       <c r="L2" t="n">
-        <v>-50655000</v>
+        <v>-19576000</v>
       </c>
       <c r="M2" t="n">
-        <v>60625000</v>
+        <v>20702000</v>
       </c>
       <c r="N2" t="n">
-        <v>4906000</v>
+        <v>1326000</v>
       </c>
       <c r="O2" t="n">
-        <v>136273915</v>
+        <v>111996202</v>
       </c>
       <c r="P2" t="n">
-        <v>109720000</v>
+        <v>83788000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1802308000</v>
+        <v>1308619000</v>
       </c>
       <c r="R2" t="n">
-        <v>197468000</v>
+        <v>147441000</v>
       </c>
       <c r="S2" t="n">
-        <v>34540000</v>
+        <v>31400000</v>
       </c>
       <c r="T2" t="n">
-        <v>34540000</v>
+        <v>31400000</v>
       </c>
       <c r="U2" t="n">
-        <v>3.18</v>
+        <v>2.67</v>
       </c>
       <c r="V2" t="n">
-        <v>3.18</v>
+        <v>2.67</v>
       </c>
       <c r="W2" t="n">
-        <v>109720000</v>
+        <v>83788000</v>
       </c>
       <c r="X2" t="n">
-        <v>109720000</v>
+        <v>83788000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>109720000</v>
+        <v>83788000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2597000</v>
+        <v>-3453000</v>
       </c>
       <c r="AB2" t="n">
-        <v>112317000</v>
+        <v>87241000</v>
       </c>
       <c r="AC2" t="n">
-        <v>112317000</v>
+        <v>87241000</v>
       </c>
       <c r="AD2" t="n">
-        <v>34496000</v>
+        <v>40624000</v>
       </c>
       <c r="AE2" t="n">
-        <v>146813000</v>
+        <v>127865000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-32622000</v>
+        <v>-41361000</v>
       </c>
       <c r="AG2" t="n">
-        <v>26542000</v>
+        <v>12861000</v>
       </c>
       <c r="AH2" t="n">
-        <v>5086000</v>
+        <v>28518000</v>
       </c>
       <c r="AI2" t="n">
-        <v>994000</v>
+        <v>-18000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-50655000</v>
+        <v>-19576000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-5064000</v>
+        <v>200000</v>
       </c>
       <c r="AL2" t="n">
-        <v>60625000</v>
+        <v>20702000</v>
       </c>
       <c r="AM2" t="n">
-        <v>4906000</v>
+        <v>1326000</v>
       </c>
       <c r="AN2" t="n">
-        <v>233595000</v>
+        <v>189388000</v>
       </c>
       <c r="AO2" t="n">
-        <v>374170000</v>
+        <v>256934000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-499000</v>
+        <v>2857000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>40628000</v>
+        <v>11291000</v>
       </c>
       <c r="AR2" t="n">
-        <v>40628000</v>
+        <v>11291000</v>
       </c>
       <c r="AS2" t="n">
-        <v>22380000</v>
+        <v>9969000</v>
       </c>
       <c r="AT2" t="n">
-        <v>341744000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>244727000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>244727000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>341744000</v>
+        <v>244727000</v>
       </c>
       <c r="AW2" t="n">
-        <v>607765000</v>
+        <v>446322000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1428138000</v>
+        <v>1051685000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2035903000</v>
+        <v>1498007000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2035903000</v>
+        <v>1498007000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45260</v>
+        <v>44895</v>
       </c>
       <c r="B3" t="n">
-        <v>-4100953</v>
+        <v>-6552984</v>
       </c>
       <c r="C3" t="n">
-        <v>0.283</v>
+        <v>0.274</v>
       </c>
       <c r="D3" t="n">
-        <v>418381000</v>
+        <v>364237000</v>
       </c>
       <c r="E3" t="n">
-        <v>-14491000</v>
+        <v>-23916000</v>
       </c>
       <c r="F3" t="n">
-        <v>-14491000</v>
+        <v>-23916000</v>
       </c>
       <c r="G3" t="n">
-        <v>116126000</v>
+        <v>96120000</v>
       </c>
       <c r="H3" t="n">
-        <v>186026000</v>
+        <v>171555000</v>
       </c>
       <c r="I3" t="n">
-        <v>1393172000</v>
+        <v>1270282000</v>
       </c>
       <c r="J3" t="n">
-        <v>403890000</v>
+        <v>340321000</v>
       </c>
       <c r="K3" t="n">
-        <v>217864000</v>
+        <v>168766000</v>
       </c>
       <c r="L3" t="n">
-        <v>-45962000</v>
+        <v>-28502000</v>
       </c>
       <c r="M3" t="n">
-        <v>50435000</v>
+        <v>27955000</v>
       </c>
       <c r="N3" t="n">
-        <v>3802000</v>
+        <v>1984000</v>
       </c>
       <c r="O3" t="n">
-        <v>126516047</v>
+        <v>113483016</v>
       </c>
       <c r="P3" t="n">
-        <v>116126000</v>
+        <v>96120000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1761017000</v>
+        <v>1623382000</v>
       </c>
       <c r="R3" t="n">
-        <v>213391000</v>
+        <v>169313000</v>
       </c>
       <c r="S3" t="n">
-        <v>33336000</v>
+        <v>31400000</v>
       </c>
       <c r="T3" t="n">
-        <v>33336000</v>
+        <v>31400000</v>
       </c>
       <c r="U3" t="n">
-        <v>3.48</v>
+        <v>3.06</v>
       </c>
       <c r="V3" t="n">
-        <v>3.48</v>
+        <v>3.06</v>
       </c>
       <c r="W3" t="n">
-        <v>116126000</v>
+        <v>96120000</v>
       </c>
       <c r="X3" t="n">
-        <v>116126000</v>
+        <v>96120000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>116126000</v>
+        <v>96120000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3959000</v>
+        <v>-6071000</v>
       </c>
       <c r="AB3" t="n">
-        <v>120085000</v>
+        <v>102191000</v>
       </c>
       <c r="AC3" t="n">
-        <v>120085000</v>
+        <v>102191000</v>
       </c>
       <c r="AD3" t="n">
-        <v>47344000</v>
+        <v>38620000</v>
       </c>
       <c r="AE3" t="n">
-        <v>167429000</v>
+        <v>140811000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-14482000</v>
+        <v>-23916000</v>
       </c>
       <c r="AG3" t="n">
-        <v>10443000</v>
+        <v>18751000</v>
       </c>
       <c r="AH3" t="n">
-        <v>4765000</v>
+        <v>5503000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-726000</v>
+        <v>-338000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-45962000</v>
+        <v>-28502000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-671000</v>
+        <v>2531000</v>
       </c>
       <c r="AL3" t="n">
-        <v>50435000</v>
+        <v>27955000</v>
       </c>
       <c r="AM3" t="n">
-        <v>3802000</v>
+        <v>1984000</v>
       </c>
       <c r="AN3" t="n">
-        <v>229469000</v>
+        <v>193712000</v>
       </c>
       <c r="AO3" t="n">
-        <v>367845000</v>
+        <v>353100000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1017000</v>
+        <v>-4965000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>41838000</v>
+        <v>41229000</v>
       </c>
       <c r="AR3" t="n">
-        <v>41838000</v>
+        <v>41229000</v>
       </c>
       <c r="AS3" t="n">
-        <v>16127000</v>
+        <v>21619000</v>
       </c>
       <c r="AT3" t="n">
-        <v>326017000</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>304637000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>304637000</v>
+      </c>
       <c r="AV3" t="n">
-        <v>326017000</v>
+        <v>304637000</v>
       </c>
       <c r="AW3" t="n">
-        <v>597314000</v>
+        <v>546812000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1393172000</v>
+        <v>1270282000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1990486000</v>
+        <v>1817094000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1990486000</v>
+        <v>1817094000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44895</v>
+        <v>45260</v>
       </c>
       <c r="B4" t="n">
-        <v>-6552984</v>
+        <v>-4100953</v>
       </c>
       <c r="C4" t="n">
-        <v>0.274</v>
+        <v>0.283</v>
       </c>
       <c r="D4" t="n">
-        <v>364237000</v>
+        <v>418381000</v>
       </c>
       <c r="E4" t="n">
-        <v>-23916000</v>
+        <v>-14491000</v>
       </c>
       <c r="F4" t="n">
-        <v>-23916000</v>
+        <v>-14491000</v>
       </c>
       <c r="G4" t="n">
-        <v>96120000</v>
+        <v>116126000</v>
       </c>
       <c r="H4" t="n">
-        <v>171555000</v>
+        <v>186026000</v>
       </c>
       <c r="I4" t="n">
-        <v>1270282000</v>
+        <v>1393172000</v>
       </c>
       <c r="J4" t="n">
-        <v>340321000</v>
+        <v>403890000</v>
       </c>
       <c r="K4" t="n">
-        <v>168766000</v>
+        <v>217864000</v>
       </c>
       <c r="L4" t="n">
-        <v>-28502000</v>
+        <v>-45962000</v>
       </c>
       <c r="M4" t="n">
-        <v>27955000</v>
+        <v>50435000</v>
       </c>
       <c r="N4" t="n">
-        <v>1984000</v>
+        <v>3802000</v>
       </c>
       <c r="O4" t="n">
-        <v>113483016</v>
+        <v>126516047</v>
       </c>
       <c r="P4" t="n">
-        <v>96120000</v>
+        <v>116126000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1623382000</v>
+        <v>1761017000</v>
       </c>
       <c r="R4" t="n">
-        <v>169313000</v>
+        <v>213391000</v>
       </c>
       <c r="S4" t="n">
-        <v>31400000</v>
+        <v>33336000</v>
       </c>
       <c r="T4" t="n">
-        <v>31400000</v>
+        <v>33336000</v>
       </c>
       <c r="U4" t="n">
-        <v>3.06</v>
+        <v>3.48</v>
       </c>
       <c r="V4" t="n">
-        <v>3.06</v>
+        <v>3.48</v>
       </c>
       <c r="W4" t="n">
-        <v>96120000</v>
+        <v>116126000</v>
       </c>
       <c r="X4" t="n">
-        <v>96120000</v>
+        <v>116126000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>96120000</v>
+        <v>116126000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-6071000</v>
+        <v>-3959000</v>
       </c>
       <c r="AB4" t="n">
-        <v>102191000</v>
+        <v>120085000</v>
       </c>
       <c r="AC4" t="n">
-        <v>102191000</v>
+        <v>120085000</v>
       </c>
       <c r="AD4" t="n">
-        <v>38620000</v>
+        <v>47344000</v>
       </c>
       <c r="AE4" t="n">
-        <v>140811000</v>
+        <v>167429000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-23916000</v>
+        <v>-14482000</v>
       </c>
       <c r="AG4" t="n">
-        <v>18751000</v>
+        <v>10443000</v>
       </c>
       <c r="AH4" t="n">
-        <v>5503000</v>
+        <v>4765000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-338000</v>
+        <v>-726000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-28502000</v>
+        <v>-45962000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2531000</v>
+        <v>-671000</v>
       </c>
       <c r="AL4" t="n">
-        <v>27955000</v>
+        <v>50435000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1984000</v>
+        <v>3802000</v>
       </c>
       <c r="AN4" t="n">
-        <v>193712000</v>
+        <v>229469000</v>
       </c>
       <c r="AO4" t="n">
-        <v>353100000</v>
+        <v>367845000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-4965000</v>
+        <v>-1017000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>41229000</v>
+        <v>41838000</v>
       </c>
       <c r="AR4" t="n">
-        <v>41229000</v>
+        <v>41838000</v>
       </c>
       <c r="AS4" t="n">
-        <v>21619000</v>
+        <v>16127000</v>
       </c>
       <c r="AT4" t="n">
-        <v>304637000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>304637000</v>
-      </c>
+        <v>326017000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>304637000</v>
+        <v>326017000</v>
       </c>
       <c r="AW4" t="n">
-        <v>546812000</v>
+        <v>597314000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1270282000</v>
+        <v>1393172000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1817094000</v>
+        <v>1990486000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1817094000</v>
+        <v>1990486000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44530</v>
+        <v>45626</v>
       </c>
       <c r="B5" t="n">
-        <v>-13152798</v>
+        <v>-8157085</v>
       </c>
       <c r="C5" t="n">
-        <v>0.318</v>
+        <v>0.235</v>
       </c>
       <c r="D5" t="n">
-        <v>335287000</v>
+        <v>440681000</v>
       </c>
       <c r="E5" t="n">
-        <v>-41361000</v>
+        <v>-34711000</v>
       </c>
       <c r="F5" t="n">
-        <v>-41361000</v>
+        <v>-34711000</v>
       </c>
       <c r="G5" t="n">
-        <v>83788000</v>
+        <v>109720000</v>
       </c>
       <c r="H5" t="n">
-        <v>145359000</v>
+        <v>198532000</v>
       </c>
       <c r="I5" t="n">
-        <v>1051685000</v>
+        <v>1428138000</v>
       </c>
       <c r="J5" t="n">
-        <v>293926000</v>
+        <v>405970000</v>
       </c>
       <c r="K5" t="n">
-        <v>148567000</v>
+        <v>207438000</v>
       </c>
       <c r="L5" t="n">
-        <v>-19576000</v>
+        <v>-50655000</v>
       </c>
       <c r="M5" t="n">
-        <v>20702000</v>
+        <v>60625000</v>
       </c>
       <c r="N5" t="n">
-        <v>1326000</v>
+        <v>4906000</v>
       </c>
       <c r="O5" t="n">
-        <v>111996202</v>
+        <v>136273915</v>
       </c>
       <c r="P5" t="n">
-        <v>83788000</v>
+        <v>109720000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1308619000</v>
+        <v>1802308000</v>
       </c>
       <c r="R5" t="n">
-        <v>147441000</v>
+        <v>197468000</v>
       </c>
       <c r="S5" t="n">
-        <v>31400000</v>
+        <v>34540000</v>
       </c>
       <c r="T5" t="n">
-        <v>31400000</v>
+        <v>34540000</v>
       </c>
       <c r="U5" t="n">
-        <v>2.67</v>
+        <v>3.18</v>
       </c>
       <c r="V5" t="n">
-        <v>2.67</v>
+        <v>3.18</v>
       </c>
       <c r="W5" t="n">
-        <v>83788000</v>
+        <v>109720000</v>
       </c>
       <c r="X5" t="n">
-        <v>83788000</v>
+        <v>109720000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>83788000</v>
+        <v>109720000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3453000</v>
+        <v>-2597000</v>
       </c>
       <c r="AB5" t="n">
-        <v>87241000</v>
+        <v>112317000</v>
       </c>
       <c r="AC5" t="n">
-        <v>87241000</v>
+        <v>112317000</v>
       </c>
       <c r="AD5" t="n">
-        <v>40624000</v>
+        <v>34496000</v>
       </c>
       <c r="AE5" t="n">
-        <v>127865000</v>
+        <v>146813000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-41361000</v>
+        <v>-32622000</v>
       </c>
       <c r="AG5" t="n">
-        <v>12861000</v>
+        <v>26542000</v>
       </c>
       <c r="AH5" t="n">
-        <v>28518000</v>
+        <v>5086000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-18000</v>
+        <v>994000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-19576000</v>
+        <v>-50655000</v>
       </c>
       <c r="AK5" t="n">
-        <v>200000</v>
+        <v>-5064000</v>
       </c>
       <c r="AL5" t="n">
-        <v>20702000</v>
+        <v>60625000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1326000</v>
+        <v>4906000</v>
       </c>
       <c r="AN5" t="n">
-        <v>189388000</v>
+        <v>233595000</v>
       </c>
       <c r="AO5" t="n">
-        <v>256934000</v>
+        <v>374170000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2857000</v>
+        <v>-499000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11291000</v>
+        <v>40628000</v>
       </c>
       <c r="AR5" t="n">
-        <v>11291000</v>
+        <v>40628000</v>
       </c>
       <c r="AS5" t="n">
-        <v>9969000</v>
+        <v>22380000</v>
       </c>
       <c r="AT5" t="n">
-        <v>244727000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>244727000</v>
-      </c>
+        <v>341744000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>244727000</v>
+        <v>341744000</v>
       </c>
       <c r="AW5" t="n">
-        <v>446322000</v>
+        <v>607765000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1051685000</v>
+        <v>1428138000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1498007000</v>
+        <v>2035903000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1498007000</v>
+        <v>2035903000</v>
       </c>
     </row>
   </sheetData>
@@ -1731,974 +1731,974 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45626</v>
+        <v>44530</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>34540000</v>
+        <v>31400000</v>
       </c>
       <c r="D2" t="n">
-        <v>34540000</v>
+        <v>31400000</v>
       </c>
       <c r="E2" t="n">
-        <v>1030342000</v>
+        <v>955899000</v>
       </c>
       <c r="F2" t="n">
-        <v>1282197000</v>
+        <v>1133683000</v>
       </c>
       <c r="G2" t="n">
-        <v>270389000</v>
+        <v>-294914000</v>
       </c>
       <c r="H2" t="n">
-        <v>2728282000</v>
+        <v>2063793000</v>
       </c>
       <c r="I2" t="n">
-        <v>6798000</v>
+        <v>-228600000</v>
       </c>
       <c r="J2" t="n">
-        <v>270389000</v>
+        <v>-294914000</v>
       </c>
       <c r="K2" t="n">
-        <v>65477000</v>
+        <v>63733000</v>
       </c>
       <c r="L2" t="n">
-        <v>1511562000</v>
+        <v>993843000</v>
       </c>
       <c r="M2" t="n">
-        <v>2382369000</v>
+        <v>1648843000</v>
       </c>
       <c r="N2" t="n">
-        <v>1539141000</v>
+        <v>1014741000</v>
       </c>
       <c r="O2" t="n">
-        <v>27579000</v>
+        <v>20898000</v>
       </c>
       <c r="P2" t="n">
-        <v>1511562000</v>
+        <v>993843000</v>
       </c>
       <c r="Q2" t="n">
-        <v>746212000</v>
+        <v>538720000</v>
       </c>
       <c r="R2" t="n">
-        <v>778475000</v>
+        <v>513827000</v>
       </c>
       <c r="S2" t="n">
-        <v>34540000</v>
+        <v>31400000</v>
       </c>
       <c r="T2" t="n">
-        <v>34540000</v>
+        <v>31400000</v>
       </c>
       <c r="U2" t="n">
-        <v>2270023000</v>
+        <v>1862727000</v>
       </c>
       <c r="V2" t="n">
-        <v>1284520000</v>
+        <v>976946000</v>
       </c>
       <c r="W2" t="n">
-        <v>2743000</v>
+        <v>17956000</v>
       </c>
       <c r="X2" t="n">
-        <v>98758000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>134928000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>506000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>122187000</v>
+        <v>1615000</v>
       </c>
       <c r="AA2" t="n">
-        <v>116343000</v>
+        <v>116184000</v>
       </c>
       <c r="AB2" t="n">
-        <v>916087000</v>
+        <v>695274000</v>
       </c>
       <c r="AC2" t="n">
-        <v>45280000</v>
+        <v>40274000</v>
       </c>
       <c r="AD2" t="n">
-        <v>870807000</v>
+        <v>655000000</v>
       </c>
       <c r="AE2" t="n">
-        <v>12736000</v>
+        <v>10389000</v>
       </c>
       <c r="AF2" t="n">
-        <v>985503000</v>
+        <v>885781000</v>
       </c>
       <c r="AG2" t="n">
-        <v>85811000</v>
+        <v>86668000</v>
       </c>
       <c r="AH2" t="n">
-        <v>366110000</v>
+        <v>438409000</v>
       </c>
       <c r="AI2" t="n">
-        <v>20197000</v>
+        <v>23459000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>345913000</v>
+        <v>414950000</v>
       </c>
       <c r="AK2" t="n">
-        <v>12589000</v>
+        <v>12462000</v>
       </c>
       <c r="AL2" t="n">
-        <v>26575000</v>
+        <v>33165000</v>
       </c>
       <c r="AM2" t="n">
-        <v>385003000</v>
+        <v>296423000</v>
       </c>
       <c r="AN2" t="n">
-        <v>30421000</v>
+        <v>12170000</v>
       </c>
       <c r="AO2" t="n">
-        <v>354582000</v>
+        <v>284253000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3809164000</v>
+        <v>2877468000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2816863000</v>
+        <v>2220287000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-19400000</v>
+        <v>461000</v>
       </c>
       <c r="AS2" t="n">
-        <v>100000</v>
+        <v>399000</v>
       </c>
       <c r="AT2" t="n">
-        <v>17384000</v>
+        <v>6348000</v>
       </c>
       <c r="AU2" t="n">
-        <v>4820000</v>
+        <v>7354000</v>
       </c>
       <c r="AV2" t="n">
-        <v>37587000</v>
+        <v>10717000</v>
       </c>
       <c r="AW2" t="n">
-        <v>37587000</v>
+        <v>10717000</v>
       </c>
       <c r="AX2" t="n">
-        <v>20513000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>20513000</v>
-      </c>
+        <v>54000</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>1752000</v>
+        <v>974000</v>
       </c>
       <c r="BB2" t="n">
-        <v>1241173000</v>
+        <v>1288757000</v>
       </c>
       <c r="BC2" t="n">
-        <v>564820000</v>
+        <v>632527000</v>
       </c>
       <c r="BD2" t="n">
-        <v>676353000</v>
+        <v>656230000</v>
       </c>
       <c r="BE2" t="n">
-        <v>1506265000</v>
+        <v>904324000</v>
       </c>
       <c r="BF2" t="n">
-        <v>-1167816000</v>
+        <v>-860745000</v>
       </c>
       <c r="BG2" t="n">
-        <v>2674081000</v>
+        <v>1765069000</v>
       </c>
       <c r="BH2" t="n">
-        <v>488112000</v>
+        <v>207844000</v>
       </c>
       <c r="BI2" t="n">
-        <v>188914000</v>
+        <v>140708000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1481767000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>57319000</v>
-      </c>
+        <v>1071148000</v>
+      </c>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
-        <v>457969000</v>
+        <v>345369000</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>992301000</v>
+        <v>657181000</v>
       </c>
       <c r="BO2" t="n">
-        <v>21873000</v>
+        <v>7806000</v>
       </c>
       <c r="BP2" t="n">
-        <v>254000</v>
+        <v>37000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3141000</v>
+        <v>383000</v>
       </c>
       <c r="BR2" t="n">
-        <v>11709000</v>
+        <v>7386000</v>
       </c>
       <c r="BS2" t="n">
-        <v>349744000</v>
+        <v>235449000</v>
       </c>
       <c r="BT2" t="n">
-        <v>163057000</v>
+        <v>120948000</v>
       </c>
       <c r="BU2" t="n">
-        <v>40127000</v>
+        <v>20082000</v>
       </c>
       <c r="BV2" t="n">
-        <v>146560000</v>
+        <v>94419000</v>
       </c>
       <c r="BW2" t="n">
-        <v>23798000</v>
+        <v>39250000</v>
       </c>
       <c r="BX2" t="n">
-        <v>58082000</v>
+        <v>24191000</v>
       </c>
       <c r="BY2" t="n">
-        <v>310641000</v>
+        <v>212385000</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-2269000</v>
+        <v>-4720000</v>
       </c>
       <c r="CA2" t="n">
-        <v>312910000</v>
+        <v>217105000</v>
       </c>
       <c r="CB2" t="n">
-        <v>213059000</v>
+        <v>130294000</v>
       </c>
       <c r="CC2" t="n">
-        <v>26681000</v>
+        <v>16243000</v>
       </c>
       <c r="CD2" t="n">
-        <v>186378000</v>
+        <v>114051000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+        <v>44895</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>34540000</v>
+        <v>31400000</v>
       </c>
       <c r="D3" t="n">
-        <v>34540000</v>
+        <v>31400000</v>
       </c>
       <c r="E3" t="n">
-        <v>856209000</v>
+        <v>1045422000</v>
       </c>
       <c r="F3" t="n">
-        <v>1041308000</v>
+        <v>1220995000</v>
       </c>
       <c r="G3" t="n">
-        <v>182663000</v>
+        <v>-74483000</v>
       </c>
       <c r="H3" t="n">
-        <v>2424208000</v>
+        <v>2401130000</v>
       </c>
       <c r="I3" t="n">
-        <v>-108392000</v>
+        <v>-291294000</v>
       </c>
       <c r="J3" t="n">
-        <v>182663000</v>
+        <v>-74483000</v>
       </c>
       <c r="K3" t="n">
-        <v>62760000</v>
+        <v>62784000</v>
       </c>
       <c r="L3" t="n">
-        <v>1445660000</v>
+        <v>1242919000</v>
       </c>
       <c r="M3" t="n">
-        <v>2058476000</v>
+        <v>1881503000</v>
       </c>
       <c r="N3" t="n">
-        <v>1472367000</v>
+        <v>1269375000</v>
       </c>
       <c r="O3" t="n">
-        <v>26707000</v>
+        <v>26456000</v>
       </c>
       <c r="P3" t="n">
-        <v>1445660000</v>
+        <v>1242919000</v>
       </c>
       <c r="Q3" t="n">
-        <v>681163000</v>
+        <v>614476000</v>
       </c>
       <c r="R3" t="n">
-        <v>778475000</v>
+        <v>513827000</v>
       </c>
       <c r="S3" t="n">
-        <v>34540000</v>
+        <v>31400000</v>
       </c>
       <c r="T3" t="n">
-        <v>34540000</v>
+        <v>31400000</v>
       </c>
       <c r="U3" t="n">
-        <v>1956772000</v>
+        <v>2084918000</v>
       </c>
       <c r="V3" t="n">
-        <v>998806000</v>
+        <v>983487000</v>
       </c>
       <c r="W3" t="n">
-        <v>2050000</v>
+        <v>1687000</v>
       </c>
       <c r="X3" t="n">
-        <v>101077000</v>
+        <v>105384000</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>94626000</v>
+        <v>19482000</v>
       </c>
       <c r="AA3" t="n">
-        <v>113818000</v>
+        <v>162831000</v>
       </c>
       <c r="AB3" t="n">
-        <v>658495000</v>
+        <v>685278000</v>
       </c>
       <c r="AC3" t="n">
-        <v>45679000</v>
+        <v>46694000</v>
       </c>
       <c r="AD3" t="n">
-        <v>612816000</v>
+        <v>638584000</v>
       </c>
       <c r="AE3" t="n">
-        <v>16259000</v>
+        <v>8750000</v>
       </c>
       <c r="AF3" t="n">
-        <v>957966000</v>
+        <v>1101431000</v>
       </c>
       <c r="AG3" t="n">
-        <v>86999000</v>
+        <v>90489000</v>
       </c>
       <c r="AH3" t="n">
-        <v>382813000</v>
+        <v>535717000</v>
       </c>
       <c r="AI3" t="n">
-        <v>17081000</v>
+        <v>16090000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>365732000</v>
+        <v>519627000</v>
       </c>
       <c r="AK3" t="n">
-        <v>13263000</v>
+        <v>11940000</v>
       </c>
       <c r="AL3" t="n">
-        <v>21475000</v>
+        <v>30697000</v>
       </c>
       <c r="AM3" t="n">
-        <v>344571000</v>
+        <v>392666000</v>
       </c>
       <c r="AN3" t="n">
-        <v>35356000</v>
+        <v>35877000</v>
       </c>
       <c r="AO3" t="n">
-        <v>309215000</v>
+        <v>356789000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3429139000</v>
+        <v>3354293000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2579565000</v>
+        <v>2544156000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1087000</v>
+        <v>1217000</v>
       </c>
       <c r="AS3" t="n">
-        <v>9000</v>
+        <v>48000</v>
       </c>
       <c r="AT3" t="n">
-        <v>7253000</v>
+        <v>6480000</v>
       </c>
       <c r="AU3" t="n">
-        <v>7570000</v>
+        <v>129100000</v>
       </c>
       <c r="AV3" t="n">
-        <v>29601000</v>
+        <v>23398000</v>
       </c>
       <c r="AW3" t="n">
-        <v>29601000</v>
+        <v>23398000</v>
       </c>
       <c r="AX3" t="n">
-        <v>47000</v>
+        <v>3449000</v>
       </c>
       <c r="AY3" t="n">
-        <v>47000</v>
+        <v>36000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>3413000</v>
       </c>
       <c r="BA3" t="n">
-        <v>1782000</v>
+        <v>974000</v>
       </c>
       <c r="BB3" t="n">
-        <v>1262997000</v>
+        <v>1317402000</v>
       </c>
       <c r="BC3" t="n">
-        <v>592876000</v>
+        <v>632560000</v>
       </c>
       <c r="BD3" t="n">
-        <v>670121000</v>
+        <v>684842000</v>
       </c>
       <c r="BE3" t="n">
-        <v>1268540000</v>
+        <v>1060915000</v>
       </c>
       <c r="BF3" t="n">
-        <v>-1080524000</v>
+        <v>-982294000</v>
       </c>
       <c r="BG3" t="n">
-        <v>2349064000</v>
+        <v>2043209000</v>
       </c>
       <c r="BH3" t="n">
-        <v>328544000</v>
+        <v>202376000</v>
       </c>
       <c r="BI3" t="n">
-        <v>174370000</v>
+        <v>158213000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1395861000</v>
+        <v>1272678000</v>
       </c>
       <c r="BK3" t="n">
-        <v>52240000</v>
+        <v>49989000</v>
       </c>
       <c r="BL3" t="n">
-        <v>450289000</v>
+        <v>409942000</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>849574000</v>
+        <v>810137000</v>
       </c>
       <c r="BO3" t="n">
-        <v>13291000</v>
+        <v>10519000</v>
       </c>
       <c r="BP3" t="n">
-        <v>316000</v>
+        <v>308000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7851000</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>10535000</v>
+        <v>12326000</v>
       </c>
       <c r="BS3" t="n">
-        <v>323343000</v>
+        <v>304380000</v>
       </c>
       <c r="BT3" t="n">
-        <v>159393000</v>
+        <v>146028000</v>
       </c>
       <c r="BU3" t="n">
-        <v>33910000</v>
+        <v>32862000</v>
       </c>
       <c r="BV3" t="n">
-        <v>130040000</v>
+        <v>125490000</v>
       </c>
       <c r="BW3" t="n">
-        <v>29216000</v>
+        <v>47209000</v>
       </c>
       <c r="BX3" t="n">
-        <v>49888000</v>
+        <v>40726000</v>
       </c>
       <c r="BY3" t="n">
-        <v>278383000</v>
+        <v>269835000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-1824000</v>
+        <v>-4101000</v>
       </c>
       <c r="CA3" t="n">
-        <v>280207000</v>
+        <v>273936000</v>
       </c>
       <c r="CB3" t="n">
-        <v>136751000</v>
+        <v>124834000</v>
       </c>
       <c r="CC3" t="n">
-        <v>14412000</v>
+        <v>12045000</v>
       </c>
       <c r="CD3" t="n">
-        <v>122339000</v>
+        <v>112789000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44895</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45260</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
-        <v>31400000</v>
+        <v>34540000</v>
       </c>
       <c r="D4" t="n">
-        <v>31400000</v>
+        <v>34540000</v>
       </c>
       <c r="E4" t="n">
-        <v>1045422000</v>
+        <v>856209000</v>
       </c>
       <c r="F4" t="n">
-        <v>1220995000</v>
+        <v>1041308000</v>
       </c>
       <c r="G4" t="n">
-        <v>-74483000</v>
+        <v>182663000</v>
       </c>
       <c r="H4" t="n">
-        <v>2401130000</v>
+        <v>2424208000</v>
       </c>
       <c r="I4" t="n">
-        <v>-291294000</v>
+        <v>-108392000</v>
       </c>
       <c r="J4" t="n">
-        <v>-74483000</v>
+        <v>182663000</v>
       </c>
       <c r="K4" t="n">
-        <v>62784000</v>
+        <v>62760000</v>
       </c>
       <c r="L4" t="n">
-        <v>1242919000</v>
+        <v>1445660000</v>
       </c>
       <c r="M4" t="n">
-        <v>1881503000</v>
+        <v>2058476000</v>
       </c>
       <c r="N4" t="n">
-        <v>1269375000</v>
+        <v>1472367000</v>
       </c>
       <c r="O4" t="n">
-        <v>26456000</v>
+        <v>26707000</v>
       </c>
       <c r="P4" t="n">
-        <v>1242919000</v>
+        <v>1445660000</v>
       </c>
       <c r="Q4" t="n">
-        <v>614476000</v>
+        <v>681163000</v>
       </c>
       <c r="R4" t="n">
-        <v>513827000</v>
+        <v>778475000</v>
       </c>
       <c r="S4" t="n">
-        <v>31400000</v>
+        <v>34540000</v>
       </c>
       <c r="T4" t="n">
-        <v>31400000</v>
+        <v>34540000</v>
       </c>
       <c r="U4" t="n">
-        <v>2084918000</v>
+        <v>1956772000</v>
       </c>
       <c r="V4" t="n">
-        <v>983487000</v>
+        <v>998806000</v>
       </c>
       <c r="W4" t="n">
-        <v>1687000</v>
+        <v>2050000</v>
       </c>
       <c r="X4" t="n">
-        <v>105384000</v>
+        <v>101077000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>19482000</v>
+        <v>94626000</v>
       </c>
       <c r="AA4" t="n">
-        <v>162831000</v>
+        <v>113818000</v>
       </c>
       <c r="AB4" t="n">
-        <v>685278000</v>
+        <v>658495000</v>
       </c>
       <c r="AC4" t="n">
-        <v>46694000</v>
+        <v>45679000</v>
       </c>
       <c r="AD4" t="n">
-        <v>638584000</v>
+        <v>612816000</v>
       </c>
       <c r="AE4" t="n">
-        <v>8750000</v>
+        <v>16259000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1101431000</v>
+        <v>957966000</v>
       </c>
       <c r="AG4" t="n">
-        <v>90489000</v>
+        <v>86999000</v>
       </c>
       <c r="AH4" t="n">
-        <v>535717000</v>
+        <v>382813000</v>
       </c>
       <c r="AI4" t="n">
-        <v>16090000</v>
+        <v>17081000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>519627000</v>
+        <v>365732000</v>
       </c>
       <c r="AK4" t="n">
-        <v>11940000</v>
+        <v>13263000</v>
       </c>
       <c r="AL4" t="n">
-        <v>30697000</v>
+        <v>21475000</v>
       </c>
       <c r="AM4" t="n">
-        <v>392666000</v>
+        <v>344571000</v>
       </c>
       <c r="AN4" t="n">
-        <v>35877000</v>
+        <v>35356000</v>
       </c>
       <c r="AO4" t="n">
-        <v>356789000</v>
+        <v>309215000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3354293000</v>
+        <v>3429139000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2544156000</v>
+        <v>2579565000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1217000</v>
+        <v>1087000</v>
       </c>
       <c r="AS4" t="n">
-        <v>48000</v>
+        <v>9000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6480000</v>
+        <v>7253000</v>
       </c>
       <c r="AU4" t="n">
-        <v>129100000</v>
+        <v>7570000</v>
       </c>
       <c r="AV4" t="n">
-        <v>23398000</v>
+        <v>29601000</v>
       </c>
       <c r="AW4" t="n">
-        <v>23398000</v>
+        <v>29601000</v>
       </c>
       <c r="AX4" t="n">
-        <v>3449000</v>
+        <v>47000</v>
       </c>
       <c r="AY4" t="n">
-        <v>36000</v>
+        <v>47000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3413000</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>974000</v>
+        <v>1782000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1317402000</v>
+        <v>1262997000</v>
       </c>
       <c r="BC4" t="n">
-        <v>632560000</v>
+        <v>592876000</v>
       </c>
       <c r="BD4" t="n">
-        <v>684842000</v>
+        <v>670121000</v>
       </c>
       <c r="BE4" t="n">
-        <v>1060915000</v>
+        <v>1268540000</v>
       </c>
       <c r="BF4" t="n">
-        <v>-982294000</v>
+        <v>-1080524000</v>
       </c>
       <c r="BG4" t="n">
-        <v>2043209000</v>
+        <v>2349064000</v>
       </c>
       <c r="BH4" t="n">
-        <v>202376000</v>
+        <v>328544000</v>
       </c>
       <c r="BI4" t="n">
-        <v>158213000</v>
+        <v>174370000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1272678000</v>
+        <v>1395861000</v>
       </c>
       <c r="BK4" t="n">
-        <v>49989000</v>
+        <v>52240000</v>
       </c>
       <c r="BL4" t="n">
-        <v>409942000</v>
+        <v>450289000</v>
       </c>
       <c r="BM4" t="n">
         <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>810137000</v>
+        <v>849574000</v>
       </c>
       <c r="BO4" t="n">
-        <v>10519000</v>
+        <v>13291000</v>
       </c>
       <c r="BP4" t="n">
-        <v>308000</v>
+        <v>316000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>7851000</v>
       </c>
       <c r="BR4" t="n">
-        <v>12326000</v>
+        <v>10535000</v>
       </c>
       <c r="BS4" t="n">
-        <v>304380000</v>
+        <v>323343000</v>
       </c>
       <c r="BT4" t="n">
-        <v>146028000</v>
+        <v>159393000</v>
       </c>
       <c r="BU4" t="n">
-        <v>32862000</v>
+        <v>33910000</v>
       </c>
       <c r="BV4" t="n">
-        <v>125490000</v>
+        <v>130040000</v>
       </c>
       <c r="BW4" t="n">
-        <v>47209000</v>
+        <v>29216000</v>
       </c>
       <c r="BX4" t="n">
-        <v>40726000</v>
+        <v>49888000</v>
       </c>
       <c r="BY4" t="n">
-        <v>269835000</v>
+        <v>278383000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-4101000</v>
+        <v>-1824000</v>
       </c>
       <c r="CA4" t="n">
-        <v>273936000</v>
+        <v>280207000</v>
       </c>
       <c r="CB4" t="n">
-        <v>124834000</v>
+        <v>136751000</v>
       </c>
       <c r="CC4" t="n">
-        <v>12045000</v>
+        <v>14412000</v>
       </c>
       <c r="CD4" t="n">
-        <v>112789000</v>
+        <v>122339000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44530</v>
+        <v>45626</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>31400000</v>
+        <v>34540000</v>
       </c>
       <c r="D5" t="n">
-        <v>31400000</v>
+        <v>34540000</v>
       </c>
       <c r="E5" t="n">
-        <v>955899000</v>
+        <v>1030342000</v>
       </c>
       <c r="F5" t="n">
-        <v>1133683000</v>
+        <v>1282197000</v>
       </c>
       <c r="G5" t="n">
-        <v>-294914000</v>
+        <v>270389000</v>
       </c>
       <c r="H5" t="n">
-        <v>2063793000</v>
+        <v>2728282000</v>
       </c>
       <c r="I5" t="n">
-        <v>-228600000</v>
+        <v>6798000</v>
       </c>
       <c r="J5" t="n">
-        <v>-294914000</v>
+        <v>270389000</v>
       </c>
       <c r="K5" t="n">
-        <v>63733000</v>
+        <v>65477000</v>
       </c>
       <c r="L5" t="n">
-        <v>993843000</v>
+        <v>1511562000</v>
       </c>
       <c r="M5" t="n">
-        <v>1648843000</v>
+        <v>2382369000</v>
       </c>
       <c r="N5" t="n">
-        <v>1014741000</v>
+        <v>1539141000</v>
       </c>
       <c r="O5" t="n">
-        <v>20898000</v>
+        <v>27579000</v>
       </c>
       <c r="P5" t="n">
-        <v>993843000</v>
+        <v>1511562000</v>
       </c>
       <c r="Q5" t="n">
-        <v>538720000</v>
+        <v>746212000</v>
       </c>
       <c r="R5" t="n">
-        <v>513827000</v>
+        <v>778475000</v>
       </c>
       <c r="S5" t="n">
-        <v>31400000</v>
+        <v>34540000</v>
       </c>
       <c r="T5" t="n">
-        <v>31400000</v>
+        <v>34540000</v>
       </c>
       <c r="U5" t="n">
-        <v>1862727000</v>
+        <v>2270023000</v>
       </c>
       <c r="V5" t="n">
-        <v>976946000</v>
+        <v>1284520000</v>
       </c>
       <c r="W5" t="n">
-        <v>17956000</v>
+        <v>2743000</v>
       </c>
       <c r="X5" t="n">
-        <v>134928000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>506000</v>
-      </c>
+        <v>98758000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>1615000</v>
+        <v>122187000</v>
       </c>
       <c r="AA5" t="n">
-        <v>116184000</v>
+        <v>116343000</v>
       </c>
       <c r="AB5" t="n">
-        <v>695274000</v>
+        <v>916087000</v>
       </c>
       <c r="AC5" t="n">
-        <v>40274000</v>
+        <v>45280000</v>
       </c>
       <c r="AD5" t="n">
-        <v>655000000</v>
+        <v>870807000</v>
       </c>
       <c r="AE5" t="n">
-        <v>10389000</v>
+        <v>12736000</v>
       </c>
       <c r="AF5" t="n">
-        <v>885781000</v>
+        <v>985503000</v>
       </c>
       <c r="AG5" t="n">
-        <v>86668000</v>
+        <v>85811000</v>
       </c>
       <c r="AH5" t="n">
-        <v>438409000</v>
+        <v>366110000</v>
       </c>
       <c r="AI5" t="n">
-        <v>23459000</v>
+        <v>20197000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>414950000</v>
+        <v>345913000</v>
       </c>
       <c r="AK5" t="n">
-        <v>12462000</v>
+        <v>12589000</v>
       </c>
       <c r="AL5" t="n">
-        <v>33165000</v>
+        <v>26575000</v>
       </c>
       <c r="AM5" t="n">
-        <v>296423000</v>
+        <v>385003000</v>
       </c>
       <c r="AN5" t="n">
-        <v>12170000</v>
+        <v>30421000</v>
       </c>
       <c r="AO5" t="n">
-        <v>284253000</v>
+        <v>354582000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2877468000</v>
+        <v>3809164000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2220287000</v>
+        <v>2816863000</v>
       </c>
       <c r="AR5" t="n">
-        <v>461000</v>
+        <v>-19400000</v>
       </c>
       <c r="AS5" t="n">
-        <v>399000</v>
+        <v>100000</v>
       </c>
       <c r="AT5" t="n">
-        <v>6348000</v>
+        <v>17384000</v>
       </c>
       <c r="AU5" t="n">
-        <v>7354000</v>
+        <v>4820000</v>
       </c>
       <c r="AV5" t="n">
-        <v>10717000</v>
+        <v>37587000</v>
       </c>
       <c r="AW5" t="n">
-        <v>10717000</v>
+        <v>37587000</v>
       </c>
       <c r="AX5" t="n">
-        <v>54000</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+        <v>20513000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>20513000</v>
+      </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>974000</v>
+        <v>1752000</v>
       </c>
       <c r="BB5" t="n">
-        <v>1288757000</v>
+        <v>1241173000</v>
       </c>
       <c r="BC5" t="n">
-        <v>632527000</v>
+        <v>564820000</v>
       </c>
       <c r="BD5" t="n">
-        <v>656230000</v>
+        <v>676353000</v>
       </c>
       <c r="BE5" t="n">
-        <v>904324000</v>
+        <v>1506265000</v>
       </c>
       <c r="BF5" t="n">
-        <v>-860745000</v>
+        <v>-1167816000</v>
       </c>
       <c r="BG5" t="n">
-        <v>1765069000</v>
+        <v>2674081000</v>
       </c>
       <c r="BH5" t="n">
-        <v>207844000</v>
+        <v>488112000</v>
       </c>
       <c r="BI5" t="n">
-        <v>140708000</v>
+        <v>188914000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1071148000</v>
-      </c>
-      <c r="BK5" t="inlineStr"/>
+        <v>1481767000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>57319000</v>
+      </c>
       <c r="BL5" t="n">
-        <v>345369000</v>
+        <v>457969000</v>
       </c>
       <c r="BM5" t="n">
         <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>657181000</v>
+        <v>992301000</v>
       </c>
       <c r="BO5" t="n">
-        <v>7806000</v>
+        <v>21873000</v>
       </c>
       <c r="BP5" t="n">
-        <v>37000</v>
+        <v>254000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>383000</v>
+        <v>3141000</v>
       </c>
       <c r="BR5" t="n">
-        <v>7386000</v>
+        <v>11709000</v>
       </c>
       <c r="BS5" t="n">
-        <v>235449000</v>
+        <v>349744000</v>
       </c>
       <c r="BT5" t="n">
-        <v>120948000</v>
+        <v>163057000</v>
       </c>
       <c r="BU5" t="n">
-        <v>20082000</v>
+        <v>40127000</v>
       </c>
       <c r="BV5" t="n">
-        <v>94419000</v>
+        <v>146560000</v>
       </c>
       <c r="BW5" t="n">
-        <v>39250000</v>
+        <v>23798000</v>
       </c>
       <c r="BX5" t="n">
-        <v>24191000</v>
+        <v>58082000</v>
       </c>
       <c r="BY5" t="n">
-        <v>212385000</v>
+        <v>310641000</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-4720000</v>
+        <v>-2269000</v>
       </c>
       <c r="CA5" t="n">
-        <v>217105000</v>
+        <v>312910000</v>
       </c>
       <c r="CB5" t="n">
-        <v>130294000</v>
+        <v>213059000</v>
       </c>
       <c r="CC5" t="n">
-        <v>16243000</v>
+        <v>26681000</v>
       </c>
       <c r="CD5" t="n">
-        <v>114051000</v>
+        <v>186378000</v>
       </c>
     </row>
   </sheetData>
@@ -2929,494 +2929,494 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45626</v>
+        <v>44530</v>
       </c>
       <c r="B2" t="n">
-        <v>-129514000</v>
+        <v>8450000</v>
       </c>
       <c r="C2" t="n">
-        <v>-1157206000</v>
+        <v>-252090000</v>
       </c>
       <c r="D2" t="n">
-        <v>1394207000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
+        <v>311478000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-369846000</v>
+        <v>-203626000</v>
       </c>
       <c r="G2" t="n">
-        <v>183941000</v>
+        <v>83587000</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>122264000</v>
+        <v>58394000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1338000</v>
+        <v>2128000</v>
       </c>
       <c r="K2" t="n">
-        <v>63015000</v>
+        <v>23065000</v>
       </c>
       <c r="L2" t="n">
-        <v>168269000</v>
+        <v>8025000</v>
       </c>
       <c r="M2" t="n">
-        <v>-1087000</v>
-      </c>
-      <c r="N2" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>59388000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>59388000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-252090000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>311478000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-197036000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>9445000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-2855000</v>
+      </c>
+      <c r="W2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>237001000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>237001000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-1157206000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1394207000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-345586000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>24823000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-563000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>8767000</v>
-      </c>
       <c r="X2" t="n">
-        <v>-9330000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+        <v>-2855000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-203626000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-203626000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>-369846000</v>
+        <v>-203626000</v>
       </c>
       <c r="AB2" t="n">
-        <v>240332000</v>
+        <v>212076000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-47571000</v>
+        <v>-45210000</v>
       </c>
       <c r="AD2" t="n">
-        <v>2877000</v>
+        <v>682000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-60375000</v>
+        <v>-18445000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-8770000</v>
+        <v>9307000</v>
       </c>
       <c r="AG2" t="n">
-        <v>48117000</v>
+        <v>50666000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-25736000</v>
+        <v>-44846000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-31151000</v>
+        <v>3487000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12475000</v>
+        <v>12047000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-8711000</v>
+        <v>-13167000</v>
       </c>
       <c r="AL2" t="n">
-        <v>34496000</v>
+        <v>40624000</v>
       </c>
       <c r="AM2" t="n">
-        <v>198532000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>198532000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>145359000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>145359000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>5444000</v>
+        <v>-6079000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>112317000</v>
+        <v>87241000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45260</v>
+        <v>44895</v>
       </c>
       <c r="B3" t="n">
-        <v>-33700000</v>
+        <v>-19558000</v>
       </c>
       <c r="C3" t="n">
-        <v>-707649000</v>
+        <v>-652566000</v>
       </c>
       <c r="D3" t="n">
-        <v>542446000</v>
+        <v>755521000</v>
       </c>
       <c r="E3" t="n">
-        <v>271610000</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-328037000</v>
+        <v>-241499000</v>
       </c>
       <c r="G3" t="n">
-        <v>122264000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-1000</v>
-      </c>
+        <v>98134000</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>98134000</v>
+        <v>83587000</v>
       </c>
       <c r="J3" t="n">
-        <v>-3122000</v>
+        <v>4548000</v>
       </c>
       <c r="K3" t="n">
-        <v>27253000</v>
+        <v>9999000</v>
       </c>
       <c r="L3" t="n">
-        <v>40348000</v>
+        <v>44239000</v>
       </c>
       <c r="M3" t="n">
-        <v>-2592000</v>
+        <v>-471000</v>
       </c>
       <c r="N3" t="n">
-        <v>271610000</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>271610000</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-165203000</v>
+        <v>102955000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-165203000</v>
+        <v>102955000</v>
       </c>
       <c r="R3" t="n">
-        <v>-707649000</v>
+        <v>-652566000</v>
       </c>
       <c r="S3" t="n">
-        <v>542446000</v>
+        <v>755521000</v>
       </c>
       <c r="T3" t="n">
-        <v>-307432000</v>
+        <v>-256181000</v>
       </c>
       <c r="U3" t="n">
-        <v>31106000</v>
+        <v>3770000</v>
       </c>
       <c r="V3" t="n">
-        <v>-10501000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
+        <v>-18452000</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-10501000</v>
+        <v>-18452000</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>-328037000</v>
+        <v>-241499000</v>
       </c>
       <c r="AB3" t="n">
-        <v>294337000</v>
+        <v>221941000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-58188000</v>
+        <v>-31690000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1819000</v>
+        <v>886000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-45854000</v>
+        <v>-22350000</v>
       </c>
       <c r="AF3" t="n">
-        <v>31776000</v>
+        <v>-47516000</v>
       </c>
       <c r="AG3" t="n">
-        <v>63935000</v>
+        <v>63922000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-21995000</v>
+        <v>-66452000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-10164000</v>
+        <v>-44986000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>21708000</v>
+        <v>24214000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-10667000</v>
+        <v>-14101000</v>
       </c>
       <c r="AL3" t="n">
-        <v>47344000</v>
+        <v>38620000</v>
       </c>
       <c r="AM3" t="n">
-        <v>186026000</v>
+        <v>171555000</v>
       </c>
       <c r="AN3" t="n">
-        <v>186026000</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>171555000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>171555000</v>
+      </c>
       <c r="AP3" t="n">
-        <v>529000</v>
+        <v>304000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>120085000</v>
+        <v>102191000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44895</v>
+        <v>45260</v>
       </c>
       <c r="B4" t="n">
-        <v>-19558000</v>
+        <v>-33700000</v>
       </c>
       <c r="C4" t="n">
-        <v>-652566000</v>
+        <v>-707649000</v>
       </c>
       <c r="D4" t="n">
-        <v>755521000</v>
+        <v>542446000</v>
       </c>
       <c r="E4" t="n">
+        <v>271610000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-328037000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>122264000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>98134000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-3122000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>27253000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>40348000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-2592000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>271610000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>271610000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-165203000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-165203000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-707649000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>542446000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-307432000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>31106000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-10501000</v>
+      </c>
+      <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
-        <v>-241499000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>98134000</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>83587000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4548000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>9999000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>44239000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-471000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>102955000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>102955000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-652566000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>755521000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-256181000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3770000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-18452000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-18452000</v>
+        <v>-10501000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>-241499000</v>
+        <v>-328037000</v>
       </c>
       <c r="AB4" t="n">
-        <v>221941000</v>
+        <v>294337000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-31690000</v>
+        <v>-58188000</v>
       </c>
       <c r="AD4" t="n">
-        <v>886000</v>
+        <v>1819000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-22350000</v>
+        <v>-45854000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-47516000</v>
+        <v>31776000</v>
       </c>
       <c r="AG4" t="n">
-        <v>63922000</v>
+        <v>63935000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-66452000</v>
+        <v>-21995000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-44986000</v>
+        <v>-10164000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24214000</v>
+        <v>21708000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-14101000</v>
+        <v>-10667000</v>
       </c>
       <c r="AL4" t="n">
-        <v>38620000</v>
+        <v>47344000</v>
       </c>
       <c r="AM4" t="n">
-        <v>171555000</v>
+        <v>186026000</v>
       </c>
       <c r="AN4" t="n">
-        <v>171555000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>171555000</v>
-      </c>
+        <v>186026000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>304000</v>
+        <v>529000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>102191000</v>
+        <v>120085000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44530</v>
+        <v>45626</v>
       </c>
       <c r="B5" t="n">
-        <v>8450000</v>
+        <v>-129514000</v>
       </c>
       <c r="C5" t="n">
-        <v>-252090000</v>
+        <v>-1157206000</v>
       </c>
       <c r="D5" t="n">
-        <v>311478000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>1394207000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
       <c r="F5" t="n">
-        <v>-203626000</v>
+        <v>-369846000</v>
       </c>
       <c r="G5" t="n">
-        <v>83587000</v>
+        <v>183941000</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>58394000</v>
+        <v>122264000</v>
       </c>
       <c r="J5" t="n">
-        <v>2128000</v>
+        <v>-1338000</v>
       </c>
       <c r="K5" t="n">
-        <v>23065000</v>
+        <v>63015000</v>
       </c>
       <c r="L5" t="n">
-        <v>8025000</v>
+        <v>168269000</v>
       </c>
       <c r="M5" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>-1087000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" t="n">
-        <v>59388000</v>
+        <v>237001000</v>
       </c>
       <c r="Q5" t="n">
-        <v>59388000</v>
+        <v>237001000</v>
       </c>
       <c r="R5" t="n">
-        <v>-252090000</v>
+        <v>-1157206000</v>
       </c>
       <c r="S5" t="n">
-        <v>311478000</v>
+        <v>1394207000</v>
       </c>
       <c r="T5" t="n">
-        <v>-197036000</v>
+        <v>-345586000</v>
       </c>
       <c r="U5" t="n">
-        <v>9445000</v>
+        <v>24823000</v>
       </c>
       <c r="V5" t="n">
-        <v>-2855000</v>
+        <v>-563000</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>8767000</v>
       </c>
       <c r="X5" t="n">
-        <v>-2855000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-203626000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-203626000</v>
-      </c>
+        <v>-9330000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>-203626000</v>
+        <v>-369846000</v>
       </c>
       <c r="AB5" t="n">
-        <v>212076000</v>
+        <v>240332000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-45210000</v>
+        <v>-47571000</v>
       </c>
       <c r="AD5" t="n">
-        <v>682000</v>
+        <v>2877000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-18445000</v>
+        <v>-60375000</v>
       </c>
       <c r="AF5" t="n">
-        <v>9307000</v>
+        <v>-8770000</v>
       </c>
       <c r="AG5" t="n">
-        <v>50666000</v>
+        <v>48117000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-44846000</v>
+        <v>-25736000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3487000</v>
+        <v>-31151000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>12047000</v>
+        <v>12475000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-13167000</v>
+        <v>-8711000</v>
       </c>
       <c r="AL5" t="n">
-        <v>40624000</v>
+        <v>34496000</v>
       </c>
       <c r="AM5" t="n">
-        <v>145359000</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>145359000</v>
-      </c>
+        <v>198532000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>198532000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>-6079000</v>
+        <v>5444000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>87241000</v>
+        <v>112317000</v>
       </c>
     </row>
   </sheetData>
@@ -3986,192 +3986,192 @@
       </c>
       <c r="DG1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="ES1" t="inlineStr">
@@ -4276,7 +4276,7 @@
         <v>7</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1735603200</v>
@@ -4298,34 +4298,34 @@
         <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>27.96</v>
+        <v>25.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.38</v>
+        <v>28.32</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.38</v>
+        <v>26.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>23.38</v>
+        <v>28.32</v>
       </c>
       <c r="AF2" t="n">
-        <v>27.96</v>
+        <v>25.28</v>
       </c>
       <c r="AG2" t="n">
-        <v>23.38</v>
+        <v>28.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>23.38</v>
+        <v>26.12</v>
       </c>
       <c r="AI2" t="n">
-        <v>23.38</v>
+        <v>28.32</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.04</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AL2" t="n">
         <v>1749168000</v>
@@ -4334,19 +4334,19 @@
         <v>0.0588</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.454</v>
+        <v>0.47</v>
       </c>
       <c r="AO2" t="n">
-        <v>39.676468</v>
+        <v>36.764706</v>
       </c>
       <c r="AP2" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AQ2" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AR2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -4355,16 +4355,16 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>23</v>
+        <v>24.02</v>
       </c>
       <c r="AV2" t="n">
-        <v>29.32</v>
+        <v>26.54</v>
       </c>
       <c r="AW2" t="n">
-        <v>931889216</v>
+        <v>863500032</v>
       </c>
       <c r="AX2" t="n">
-        <v>935343200</v>
+        <v>884224000</v>
       </c>
       <c r="AY2" t="n">
         <v>15.8</v>
@@ -4379,19 +4379,19 @@
         <v>15.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.41412437</v>
+        <v>0.38373277</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.8514</v>
+        <v>23.239</v>
       </c>
       <c r="BE2" t="n">
-        <v>27.8812</v>
+        <v>26.6367</v>
       </c>
       <c r="BF2" t="n">
         <v>0.04</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.0014306152</v>
+        <v>0.0015822784</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3122513152</v>
+        <v>3054124032</v>
       </c>
       <c r="BK2" t="n">
         <v>0.01038</v>
@@ -4417,7 +4417,7 @@
         <v>0.101730004</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.94482005</v>
+        <v>0.93105006</v>
       </c>
       <c r="BP2" t="n">
         <v>34540000</v>
@@ -4426,7 +4426,7 @@
         <v>40.587</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.6647448500000001</v>
+        <v>0.6159608</v>
       </c>
       <c r="BS2" t="n">
         <v>1732924800</v>
@@ -4444,16 +4444,16 @@
         <v>0.68</v>
       </c>
       <c r="BX2" t="n">
-        <v>1.388</v>
+        <v>1.357</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.111000000000001</v>
+        <v>7.933</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.49873632</v>
+        <v>-0.45071608</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="CB2" t="n">
         <v>0.04</v>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>26.98</v>
+        <v>25</v>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
@@ -4566,141 +4566,141 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>1752822000000</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.2800007</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>26.12 - 28.32</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>8</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.5822785</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>15.8 - 48.82</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>-23.82</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.4879148</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-45.07161</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1782401400</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1782401400</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1760083200</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1760083200</v>
+      </c>
+      <c r="DW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1.7609997</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.07577776999999999</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-1.6366997</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.06144529</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>finmb_144218</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="EI2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="EK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-1.1075976</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>25</v>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>Gerresheimer</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DH2" t="n">
-        <v>1777039387</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>finmb_144218</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="DO2" t="b">
+      <c r="EQ2" t="n">
+        <v>1780489391</v>
+      </c>
+      <c r="ER2" t="b">
         <v>0</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-3.5050056</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>26.98</v>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1752822000000</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.97999954</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>23.38 - 23.38</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>9</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>11.179999</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.7075949</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>15.8 - 48.82</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>-21.84</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.44735765</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-49.87363</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1781105400</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1781105400</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1760083200</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1760083200</v>
-      </c>
-      <c r="EI2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>6.128599</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.29391786</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>-0.90120125</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-0.0323229</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>Gerresheimer</t>
-        </is>
       </c>
       <c r="ES2" t="inlineStr"/>
     </row>
